--- a/per-stock/SBGSY/financials.xlsx
+++ b/per-stock/SBGSY/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>171884773376</v>
+        <v>188210954240</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>49860329472</v>
+        <v>203678892032</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.66845</v>
+        <v>36.17838</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.26352</v>
+        <v>25.74231</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.2808523</v>
+        <v>4.687462</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -715,7 +724,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>yfinance info.freeCashflow (FALLBACK levered estimate — statement TTM unavailable)</t>
         </is>
       </c>
     </row>
@@ -726,7 +735,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2813632095</v>
+        <v>2812056665</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>61.09</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,459 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → None</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D53</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C53</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B53</f>
+        <v/>
+      </c>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D51</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C51</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B51</f>
+        <v/>
+      </c>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D42</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C42</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B42</f>
+        <v/>
+      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1890,13 +2352,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1911,7 +2373,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3385,7 +3847,1081 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>14899626</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>13895647</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>14659991</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>562222886</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>561736029</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>560971685</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>577122512</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>575631676</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>575631676</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>13246000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>11546000000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>7944000000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>17880000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>15559000000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>14831000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>-6881000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>-4300000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>-2072000000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>42079000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>42509000000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>45320000000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>3532000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2621000000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>4423000000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>-6881000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>-4300000000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>-2072000000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>24199000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>26950000000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>30489000000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>39220000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>37868000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>41399000000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>24455000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>27778000000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>31280000000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>256000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>828000000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>791000000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>24199000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>26950000000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>30489000000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n">
+        <v>24117000000</v>
+      </c>
+      <c r="D16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>2844000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>2579000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>3354000000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>2308000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>2303000000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>2303000000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>2308000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>2303000000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>2303000000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>38049000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>34188000000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>34663000000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>19543000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>15250000000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>15094000000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1525000000</v>
+      </c>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n">
+        <v>1025000000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Non Current Pension And Other Postretirement Benefit Plans</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>1048000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1037000000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1098000000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>813000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>802000000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>810000000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>15021000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>10918000000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>10910000000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>15021000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>10918000000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>10910000000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Long Term Provisions</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>1136000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1178000000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>1251000000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>18506000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>18938000000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>19569000000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>1572000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1674000000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1688000000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>2859000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>4641000000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>3921000000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>2859000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>4641000000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>3921000000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Provisions</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1074000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>899000000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1052000000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>13001000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>11724000000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>12908000000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>3674000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>3330000000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>4015000000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>9327000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>8394000000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>8893000000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>62504000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>61966000000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>65943000000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>40466000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>40407000000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>41951000000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>1567000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>1717000000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>1794000000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Investmentin Financial Assets</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>1633000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>1719000000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>1601000000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Available For Sale Securities</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>1422000000</v>
+      </c>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n">
+        <v>1356000000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Financial Assets Designatedas Fair Value Through Profitor Loss Total</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>211000000</v>
+      </c>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n">
+        <v>245000000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Long Term Equity Investment</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>705000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>741000000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>1111000000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>31080000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>31250000000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>32561000000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>5938000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>6077000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>6280000000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>25142000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>25173000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>26281000000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>5481000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>4980000000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>4884000000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>-7386000000</v>
+      </c>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="3" t="n">
+        <v>-7400000000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>12867000000</v>
+      </c>
+      <c r="C48" s="3" t="n"/>
+      <c r="D48" s="3" t="n">
+        <v>12284000000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>5034000000</v>
+      </c>
+      <c r="C49" s="3" t="n"/>
+      <c r="D49" s="3" t="n">
+        <v>4504000000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>5339000000</v>
+      </c>
+      <c r="C50" s="3" t="n"/>
+      <c r="D50" s="3" t="n">
+        <v>5361000000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>2324000000</v>
+      </c>
+      <c r="C51" s="3" t="n"/>
+      <c r="D51" s="3" t="n">
+        <v>2239000000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>170000000</v>
+      </c>
+      <c r="C52" s="3" t="n"/>
+      <c r="D52" s="3" t="n">
+        <v>180000000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n"/>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>22038000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>21559000000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>23992000000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Hedging Assets Current</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>276000000</v>
+      </c>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="n">
+        <v>131000000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Assets Held For Sale Current</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>601000000</v>
+      </c>
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="3" t="n">
+        <v>589000000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>5368000000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>5866000000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>5411000000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>999000000</v>
+      </c>
+      <c r="C59" s="3" t="n"/>
+      <c r="D59" s="3" t="n">
+        <v>998000000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>2288000000</v>
+      </c>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="3" t="n">
+        <v>2160000000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>2081000000</v>
+      </c>
+      <c r="C61" s="3" t="n"/>
+      <c r="D61" s="3" t="n">
+        <v>2253000000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>2943000000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>2695000000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>2481000000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Taxes Receivable</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>995000000</v>
+      </c>
+      <c r="C63" s="3" t="n"/>
+      <c r="D63" s="3" t="n">
+        <v>1213000000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>7221000000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>8985000000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>7280000000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>4634000000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>4013000000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>6887000000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>4634000000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>4013000000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>6887000000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>2632000000</v>
+      </c>
+      <c r="C67" s="3" t="n"/>
+      <c r="D67" s="3" t="n">
+        <v>5005000000</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Cash Financial</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>2002000000</v>
+      </c>
+      <c r="C68" s="3" t="n"/>
+      <c r="D68" s="3" t="n">
+        <v>1882000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4345,7 +5881,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4366,7 +5902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4394,12 +5930,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FY Summary</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>no gaps detected</t>
+          <t>TTM uses only 0 quarters (&lt;4 available)</t>
         </is>
       </c>
     </row>
